--- a/artfynd/A 18019-2022 artfynd.xlsx
+++ b/artfynd/A 18019-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118936947</v>
+        <v>118936948</v>
       </c>
       <c r="B2" t="n">
         <v>82270</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587636</v>
+        <v>587637</v>
       </c>
       <c r="R2" t="n">
-        <v>7092825</v>
+        <v>7092835</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118936948</v>
+        <v>118936947</v>
       </c>
       <c r="B4" t="n">
         <v>82270</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587637</v>
+        <v>587636</v>
       </c>
       <c r="R4" t="n">
-        <v>7092835</v>
+        <v>7092825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18019-2022 artfynd.xlsx
+++ b/artfynd/A 18019-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118936946</v>
+        <v>118936945</v>
       </c>
       <c r="B2" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587638</v>
+        <v>587867</v>
       </c>
       <c r="R2" t="n">
-        <v>7092845</v>
+        <v>7092809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118936948</v>
+        <v>118936946</v>
       </c>
       <c r="B3" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587637</v>
+        <v>587638</v>
       </c>
       <c r="R3" t="n">
-        <v>7092835</v>
+        <v>7092845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,12 +880,7 @@
         <v>118936947</v>
       </c>
       <c r="B4" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,6 +971,208 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118936948</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övra, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587637</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118936949</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101299</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Övra, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587547</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092883</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 18019-2022 artfynd.xlsx
+++ b/artfynd/A 18019-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936945</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936947</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118936949</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>